--- a/reports/集团总公司_利润表_2025-02.xlsx
+++ b/reports/集团总公司_利润表_2025-02.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>193309691</v>
+        <v>210079924</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>147120487</v>
+        <v>158962082</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>293336705</v>
+        <v>318196257</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>599252</v>
+        <v>775126</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1199005</v>
+        <v>1547586</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>517974</v>
+        <v>679344</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>1038991</v>
+        <v>1356381</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>439912</v>
+        <v>574122</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>879316</v>
+        <v>1146637</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>402566</v>
+        <v>530227</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>807935</v>
+        <v>1059549</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>219734</v>
+        <v>291547</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>438720</v>
+        <v>583027</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>175027</v>
+        <v>229507</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>350850</v>
+        <v>459276</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>190955226</v>
+        <v>207000051</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>144766022</v>
+        <v>155882209</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>74387700</v>
+        <v>81454236</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>148445420</v>
+        <v>163203481</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1367352</v>
+        <v>2412048</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>2728702</v>
+        <v>4829413</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1233626</v>
+        <v>1752832</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>2467526</v>
+        <v>3508714</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>66313784</v>
+        <v>69158011</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>132026207</v>
+        <v>138310468</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1404084</v>
+        <v>1754324</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>2819705</v>
+        <v>3505706</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>619418</v>
+        <v>878883</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>1234843</v>
+        <v>1755403</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2191437</v>
+        <v>2641689</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>4404023</v>
+        <v>5272840</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>970438</v>
+        <v>1322107</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>1938981</v>
+        <v>2639645</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>46019519</v>
+        <v>46264831</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>92054855</v>
+        <v>92508521</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>169685</v>
+        <v>170677</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>339829</v>
+        <v>341151</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2810066</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>5617358</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1872268</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>3745382</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>139755359</v>
+        <v>158064853</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>112055411</v>
+        <v>118087917</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>88302095</v>
+        <v>94370844</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>175930358</v>
+        <v>189078723</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>23753316</v>
+        <v>23717073</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>47693922</v>
+        <v>47464155</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>4646541</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>9305675</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1486211</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>2974776</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>929145</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>1858456</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1116062</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>2230721</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>838297</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>1674526</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>559843</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1117871</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>467327</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>933046</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>2604650</v>
+        <v>2605660</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>5192571</v>
+        <v>5204858</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1217051</v>
+        <v>1228351</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>2444071</v>
+        <v>2452283</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>3173949</v>
+        <v>3176450</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>6331763</v>
+        <v>6358645</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>20452227</v>
+        <v>20529730</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>40968991</v>
+        <v>41114535</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>349293</v>
+        <v>2502172</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>697803</v>
+        <v>5015258</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1119829</v>
+        <v>1119498</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>2236657</v>
+        <v>2242547</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1157065</v>
+        <v>1069396</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>2317213</v>
+        <v>2141549</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>120353</v>
+        <v>119694</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>239868</v>
+        <v>239797</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>475166</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>951559</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>812768</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>1626680</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>316783</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>633561</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>237838</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>475335</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>397011</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>792988</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1166613</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>2329374</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>212465</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>424202</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>159551</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>318633</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>266097</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>531676</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>186257</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>372401</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>132938</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>265986</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>106207</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>212639</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>79520</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>159283</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>51199867</v>
+        <v>51922043</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>55416561</v>
+        <v>55092599</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>464565</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>930269</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>131943</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>264049</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>210941</v>
+        <v>209221</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>420778</v>
+        <v>418399</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>50988926</v>
+        <v>52177387</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7136047</v>
+        <v>7091187</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>14228901</v>
+        <v>14163604</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>43852879</v>
+        <v>45086200</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>43852879</v>
+        <v>45086200</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>43852879</v>
+        <v>45086200</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>43852879</v>
+        <v>45086200</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>43852879</v>
+        <v>45086200</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
